--- a/backend/sample_results.xlsx
+++ b/backend/sample_results.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Result_Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,113 +397,1707 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:AM20"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>USN</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Mathematics</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Physics</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Chemistry</v>
+        <v>KLE Society's</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>John Doe</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1MS20IS001</v>
-      </c>
-      <c r="C2">
-        <v>85</v>
-      </c>
-      <c r="D2">
-        <v>78</v>
-      </c>
-      <c r="E2">
-        <v>92</v>
+        <v>KLE College of Engineering and Technology,Chikodi-591201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jane Smith</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1MS20IS002</v>
-      </c>
-      <c r="C3">
-        <v>95</v>
-      </c>
-      <c r="D3">
-        <v>88</v>
-      </c>
-      <c r="E3">
-        <v>96</v>
+        <v>Department of Computer Science and Engineering</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Bob Johnson</v>
-      </c>
-      <c r="B4" t="str">
-        <v>1MS20IS003</v>
-      </c>
-      <c r="C4">
-        <v>35</v>
-      </c>
-      <c r="D4">
-        <v>45</v>
-      </c>
-      <c r="E4">
-        <v>50</v>
+        <v>4th Sem Result sheet 2025-2026 [Before Revaluation.]</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Alice Williams</v>
-      </c>
-      <c r="B5" t="str">
-        <v>1MS20IS004</v>
-      </c>
-      <c r="C5">
+        <v>Results Annouced Date : 24-07-2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Sl. No</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Std. Name</v>
+      </c>
+      <c r="C7" t="str">
+        <v>USN</v>
+      </c>
+      <c r="D7" t="str">
+        <v>BCS401</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>BCS402</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>BCS403</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>BCSL404</v>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v>BBOC407</v>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v>BUHK408</v>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <v>BNSK459</v>
+      </c>
+      <c r="AC7" t="str">
+        <v/>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v/>
+      </c>
+      <c r="AF7" t="str">
+        <v>BCS405A</v>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
+      <c r="AJ7" t="str">
+        <v>BCS456C</v>
+      </c>
+      <c r="AK7" t="str">
+        <v/>
+      </c>
+      <c r="AL7" t="str">
+        <v/>
+      </c>
+      <c r="AM7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="E8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="F8" t="str">
+        <v>T</v>
+      </c>
+      <c r="G8" t="str">
+        <v>R</v>
+      </c>
+      <c r="H8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="I8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="J8" t="str">
+        <v>T</v>
+      </c>
+      <c r="K8" t="str">
+        <v>R</v>
+      </c>
+      <c r="L8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="M8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="N8" t="str">
+        <v>T</v>
+      </c>
+      <c r="O8" t="str">
+        <v>R</v>
+      </c>
+      <c r="P8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="R8" t="str">
+        <v>T</v>
+      </c>
+      <c r="S8" t="str">
+        <v>R</v>
+      </c>
+      <c r="T8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="U8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="V8" t="str">
+        <v>T</v>
+      </c>
+      <c r="W8" t="str">
+        <v>R</v>
+      </c>
+      <c r="X8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>T</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>R</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>T</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>R</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="AG8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="AH8" t="str">
+        <v>T</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>R</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v>IN</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>EX</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>T</v>
+      </c>
+      <c r="AM8" t="str">
+        <v>R</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Kumar Mallesh Shrikhande</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2KD23CS037</v>
+      </c>
+      <c r="D9">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>60</v>
+      </c>
+      <c r="G9" t="str">
+        <v>P</v>
+      </c>
+      <c r="H9">
+        <v>35</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+      <c r="J9">
+        <v>65</v>
+      </c>
+      <c r="K9" t="str">
+        <v>P</v>
+      </c>
+      <c r="L9">
+        <v>35</v>
+      </c>
+      <c r="M9">
+        <v>35</v>
+      </c>
+      <c r="N9">
         <v>70</v>
       </c>
-      <c r="D5">
+      <c r="O9" t="str">
+        <v>P</v>
+      </c>
+      <c r="P9">
+        <v>35</v>
+      </c>
+      <c r="Q9">
+        <v>40</v>
+      </c>
+      <c r="R9">
+        <v>75</v>
+      </c>
+      <c r="S9" t="str">
+        <v>P</v>
+      </c>
+      <c r="T9">
+        <v>35</v>
+      </c>
+      <c r="U9">
+        <v>45</v>
+      </c>
+      <c r="V9">
+        <v>80</v>
+      </c>
+      <c r="W9" t="str">
+        <v>P</v>
+      </c>
+      <c r="X9">
+        <v>35</v>
+      </c>
+      <c r="Y9">
+        <v>25</v>
+      </c>
+      <c r="Z9">
+        <v>60</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB9">
+        <v>35</v>
+      </c>
+      <c r="AC9">
+        <v>30</v>
+      </c>
+      <c r="AD9">
         <v>65</v>
       </c>
-      <c r="E5">
+      <c r="AE9" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF9">
+        <v>35</v>
+      </c>
+      <c r="AG9">
+        <v>35</v>
+      </c>
+      <c r="AH9">
+        <v>70</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ9">
+        <v>35</v>
+      </c>
+      <c r="AK9">
+        <v>40</v>
+      </c>
+      <c r="AL9">
+        <v>75</v>
+      </c>
+      <c r="AM9" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Abhishek Kumar Jha</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2KD24CS001</v>
+      </c>
+      <c r="D10">
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>64</v>
+      </c>
+      <c r="G10" t="str">
+        <v>P</v>
+      </c>
+      <c r="H10">
+        <v>36</v>
+      </c>
+      <c r="I10">
+        <v>33</v>
+      </c>
+      <c r="J10">
+        <v>69</v>
+      </c>
+      <c r="K10" t="str">
+        <v>P</v>
+      </c>
+      <c r="L10">
+        <v>36</v>
+      </c>
+      <c r="M10">
+        <v>38</v>
+      </c>
+      <c r="N10">
+        <v>74</v>
+      </c>
+      <c r="O10" t="str">
+        <v>P</v>
+      </c>
+      <c r="P10">
+        <v>36</v>
+      </c>
+      <c r="Q10">
+        <v>43</v>
+      </c>
+      <c r="R10">
+        <v>79</v>
+      </c>
+      <c r="S10" t="str">
+        <v>P</v>
+      </c>
+      <c r="T10">
+        <v>36</v>
+      </c>
+      <c r="U10">
+        <v>48</v>
+      </c>
+      <c r="V10">
+        <v>84</v>
+      </c>
+      <c r="W10" t="str">
+        <v>P</v>
+      </c>
+      <c r="X10">
+        <v>36</v>
+      </c>
+      <c r="Y10">
+        <v>28</v>
+      </c>
+      <c r="Z10">
+        <v>64</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB10">
+        <v>36</v>
+      </c>
+      <c r="AC10">
+        <v>33</v>
+      </c>
+      <c r="AD10">
+        <v>69</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF10">
+        <v>36</v>
+      </c>
+      <c r="AG10">
+        <v>38</v>
+      </c>
+      <c r="AH10">
+        <v>74</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ10">
+        <v>36</v>
+      </c>
+      <c r="AK10">
+        <v>43</v>
+      </c>
+      <c r="AL10">
+        <v>79</v>
+      </c>
+      <c r="AM10" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Abhishek B Dille</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2KD24CS002</v>
+      </c>
+      <c r="D11">
+        <v>37</v>
+      </c>
+      <c r="E11">
+        <v>31</v>
+      </c>
+      <c r="F11">
+        <v>68</v>
+      </c>
+      <c r="G11" t="str">
+        <v>P</v>
+      </c>
+      <c r="H11">
+        <v>37</v>
+      </c>
+      <c r="I11">
+        <v>36</v>
+      </c>
+      <c r="J11">
+        <v>73</v>
+      </c>
+      <c r="K11" t="str">
+        <v>P</v>
+      </c>
+      <c r="L11">
+        <v>37</v>
+      </c>
+      <c r="M11">
+        <v>41</v>
+      </c>
+      <c r="N11">
+        <v>78</v>
+      </c>
+      <c r="O11" t="str">
+        <v>P</v>
+      </c>
+      <c r="P11">
+        <v>37</v>
+      </c>
+      <c r="Q11">
+        <v>46</v>
+      </c>
+      <c r="R11">
+        <v>83</v>
+      </c>
+      <c r="S11" t="str">
+        <v>P</v>
+      </c>
+      <c r="T11">
+        <v>37</v>
+      </c>
+      <c r="U11">
+        <v>26</v>
+      </c>
+      <c r="V11">
+        <v>63</v>
+      </c>
+      <c r="W11" t="str">
+        <v>P</v>
+      </c>
+      <c r="X11">
+        <v>37</v>
+      </c>
+      <c r="Y11">
+        <v>31</v>
+      </c>
+      <c r="Z11">
+        <v>68</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB11">
+        <v>37</v>
+      </c>
+      <c r="AC11">
+        <v>36</v>
+      </c>
+      <c r="AD11">
+        <v>73</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF11">
+        <v>37</v>
+      </c>
+      <c r="AG11">
+        <v>41</v>
+      </c>
+      <c r="AH11">
+        <v>78</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ11">
+        <v>37</v>
+      </c>
+      <c r="AK11">
+        <v>46</v>
+      </c>
+      <c r="AL11">
+        <v>83</v>
+      </c>
+      <c r="AM11" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Aman Mudhol</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2KD24CS003</v>
+      </c>
+      <c r="D12">
+        <v>38</v>
+      </c>
+      <c r="E12">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>72</v>
+      </c>
+      <c r="G12" t="str">
+        <v>P</v>
+      </c>
+      <c r="H12">
+        <v>38</v>
+      </c>
+      <c r="I12">
+        <v>39</v>
+      </c>
+      <c r="J12">
+        <v>77</v>
+      </c>
+      <c r="K12" t="str">
+        <v>P</v>
+      </c>
+      <c r="L12">
+        <v>38</v>
+      </c>
+      <c r="M12">
+        <v>44</v>
+      </c>
+      <c r="N12">
+        <v>82</v>
+      </c>
+      <c r="O12" t="str">
+        <v>P</v>
+      </c>
+      <c r="P12">
+        <v>38</v>
+      </c>
+      <c r="Q12">
+        <v>49</v>
+      </c>
+      <c r="R12">
+        <v>87</v>
+      </c>
+      <c r="S12" t="str">
+        <v>P</v>
+      </c>
+      <c r="T12">
+        <v>38</v>
+      </c>
+      <c r="U12">
+        <v>29</v>
+      </c>
+      <c r="V12">
+        <v>67</v>
+      </c>
+      <c r="W12" t="str">
+        <v>P</v>
+      </c>
+      <c r="X12">
+        <v>38</v>
+      </c>
+      <c r="Y12">
+        <v>34</v>
+      </c>
+      <c r="Z12">
+        <v>72</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB12">
+        <v>38</v>
+      </c>
+      <c r="AC12">
+        <v>39</v>
+      </c>
+      <c r="AD12">
+        <v>77</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF12">
+        <v>38</v>
+      </c>
+      <c r="AG12">
+        <v>44</v>
+      </c>
+      <c r="AH12">
+        <v>82</v>
+      </c>
+      <c r="AI12" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ12">
+        <v>38</v>
+      </c>
+      <c r="AK12">
+        <v>49</v>
+      </c>
+      <c r="AL12">
+        <v>87</v>
+      </c>
+      <c r="AM12" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Aishwarya R Pujari</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2KD24CS004</v>
+      </c>
+      <c r="D13">
+        <v>39</v>
+      </c>
+      <c r="E13">
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>76</v>
+      </c>
+      <c r="G13" t="str">
+        <v>P</v>
+      </c>
+      <c r="H13">
+        <v>39</v>
+      </c>
+      <c r="I13">
+        <v>42</v>
+      </c>
+      <c r="J13">
+        <v>81</v>
+      </c>
+      <c r="K13" t="str">
+        <v>P</v>
+      </c>
+      <c r="L13">
+        <v>39</v>
+      </c>
+      <c r="M13">
+        <v>47</v>
+      </c>
+      <c r="N13">
+        <v>86</v>
+      </c>
+      <c r="O13" t="str">
+        <v>P</v>
+      </c>
+      <c r="P13">
+        <v>39</v>
+      </c>
+      <c r="Q13">
+        <v>27</v>
+      </c>
+      <c r="R13">
+        <v>66</v>
+      </c>
+      <c r="S13" t="str">
+        <v>P</v>
+      </c>
+      <c r="T13">
+        <v>39</v>
+      </c>
+      <c r="U13">
+        <v>32</v>
+      </c>
+      <c r="V13">
+        <v>71</v>
+      </c>
+      <c r="W13" t="str">
+        <v>P</v>
+      </c>
+      <c r="X13">
+        <v>39</v>
+      </c>
+      <c r="Y13">
+        <v>37</v>
+      </c>
+      <c r="Z13">
+        <v>76</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB13">
+        <v>39</v>
+      </c>
+      <c r="AC13">
+        <v>42</v>
+      </c>
+      <c r="AD13">
+        <v>81</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF13">
+        <v>39</v>
+      </c>
+      <c r="AG13">
+        <v>47</v>
+      </c>
+      <c r="AH13">
+        <v>86</v>
+      </c>
+      <c r="AI13" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ13">
+        <v>39</v>
+      </c>
+      <c r="AK13">
+        <v>27</v>
+      </c>
+      <c r="AL13">
+        <v>66</v>
+      </c>
+      <c r="AM13" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Akash L Badiger</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2KD24CS005</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>40</v>
+      </c>
+      <c r="F14">
         <v>80</v>
       </c>
+      <c r="G14" t="str">
+        <v>P</v>
+      </c>
+      <c r="H14">
+        <v>40</v>
+      </c>
+      <c r="I14">
+        <v>45</v>
+      </c>
+      <c r="J14">
+        <v>85</v>
+      </c>
+      <c r="K14" t="str">
+        <v>P</v>
+      </c>
+      <c r="L14">
+        <v>40</v>
+      </c>
+      <c r="M14">
+        <v>25</v>
+      </c>
+      <c r="N14">
+        <v>65</v>
+      </c>
+      <c r="O14" t="str">
+        <v>P</v>
+      </c>
+      <c r="P14">
+        <v>40</v>
+      </c>
+      <c r="Q14">
+        <v>30</v>
+      </c>
+      <c r="R14">
+        <v>70</v>
+      </c>
+      <c r="S14" t="str">
+        <v>P</v>
+      </c>
+      <c r="T14">
+        <v>40</v>
+      </c>
+      <c r="U14">
+        <v>35</v>
+      </c>
+      <c r="V14">
+        <v>75</v>
+      </c>
+      <c r="W14" t="str">
+        <v>P</v>
+      </c>
+      <c r="X14">
+        <v>40</v>
+      </c>
+      <c r="Y14">
+        <v>40</v>
+      </c>
+      <c r="Z14">
+        <v>80</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB14">
+        <v>40</v>
+      </c>
+      <c r="AC14">
+        <v>45</v>
+      </c>
+      <c r="AD14">
+        <v>85</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF14">
+        <v>40</v>
+      </c>
+      <c r="AG14">
+        <v>25</v>
+      </c>
+      <c r="AH14">
+        <v>65</v>
+      </c>
+      <c r="AI14" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ14">
+        <v>40</v>
+      </c>
+      <c r="AK14">
+        <v>30</v>
+      </c>
+      <c r="AL14">
+        <v>70</v>
+      </c>
+      <c r="AM14" t="str">
+        <v>P</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Charlie Brown</v>
-      </c>
-      <c r="B6" t="str">
-        <v>1MS20IS005</v>
-      </c>
-      <c r="C6">
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Akash Badradhar</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2KD24CS006</v>
+      </c>
+      <c r="D15">
+        <v>41</v>
+      </c>
+      <c r="E15">
+        <v>43</v>
+      </c>
+      <c r="F15">
+        <v>84</v>
+      </c>
+      <c r="G15" t="str">
+        <v>P</v>
+      </c>
+      <c r="H15">
+        <v>41</v>
+      </c>
+      <c r="I15">
+        <v>48</v>
+      </c>
+      <c r="J15">
+        <v>89</v>
+      </c>
+      <c r="K15" t="str">
+        <v>P</v>
+      </c>
+      <c r="L15">
+        <v>41</v>
+      </c>
+      <c r="M15">
+        <v>28</v>
+      </c>
+      <c r="N15">
+        <v>69</v>
+      </c>
+      <c r="O15" t="str">
+        <v>P</v>
+      </c>
+      <c r="P15">
+        <v>41</v>
+      </c>
+      <c r="Q15">
+        <v>33</v>
+      </c>
+      <c r="R15">
+        <v>74</v>
+      </c>
+      <c r="S15" t="str">
+        <v>P</v>
+      </c>
+      <c r="T15">
+        <v>41</v>
+      </c>
+      <c r="U15">
+        <v>38</v>
+      </c>
+      <c r="V15">
+        <v>79</v>
+      </c>
+      <c r="W15" t="str">
+        <v>P</v>
+      </c>
+      <c r="X15">
+        <v>41</v>
+      </c>
+      <c r="Y15">
+        <v>43</v>
+      </c>
+      <c r="Z15">
+        <v>84</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB15">
+        <v>41</v>
+      </c>
+      <c r="AC15">
+        <v>48</v>
+      </c>
+      <c r="AD15">
+        <v>89</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF15">
+        <v>41</v>
+      </c>
+      <c r="AG15">
+        <v>28</v>
+      </c>
+      <c r="AH15">
+        <v>69</v>
+      </c>
+      <c r="AI15" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ15">
+        <v>41</v>
+      </c>
+      <c r="AK15">
+        <v>33</v>
+      </c>
+      <c r="AL15">
+        <v>74</v>
+      </c>
+      <c r="AM15" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Akash Ramesh Kar</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2KD24CS007</v>
+      </c>
+      <c r="D16">
+        <v>42</v>
+      </c>
+      <c r="E16">
+        <v>46</v>
+      </c>
+      <c r="F16">
+        <v>88</v>
+      </c>
+      <c r="G16" t="str">
+        <v>P</v>
+      </c>
+      <c r="H16">
+        <v>42</v>
+      </c>
+      <c r="I16">
+        <v>26</v>
+      </c>
+      <c r="J16">
+        <v>68</v>
+      </c>
+      <c r="K16" t="str">
+        <v>P</v>
+      </c>
+      <c r="L16">
+        <v>42</v>
+      </c>
+      <c r="M16">
+        <v>31</v>
+      </c>
+      <c r="N16">
+        <v>73</v>
+      </c>
+      <c r="O16" t="str">
+        <v>P</v>
+      </c>
+      <c r="P16">
+        <v>42</v>
+      </c>
+      <c r="Q16">
+        <v>36</v>
+      </c>
+      <c r="R16">
+        <v>78</v>
+      </c>
+      <c r="S16" t="str">
+        <v>P</v>
+      </c>
+      <c r="T16">
+        <v>42</v>
+      </c>
+      <c r="U16">
+        <v>41</v>
+      </c>
+      <c r="V16">
+        <v>83</v>
+      </c>
+      <c r="W16" t="str">
+        <v>P</v>
+      </c>
+      <c r="X16">
+        <v>42</v>
+      </c>
+      <c r="Y16">
+        <v>46</v>
+      </c>
+      <c r="Z16">
+        <v>88</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB16">
+        <v>42</v>
+      </c>
+      <c r="AC16">
+        <v>26</v>
+      </c>
+      <c r="AD16">
+        <v>68</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF16">
+        <v>42</v>
+      </c>
+      <c r="AG16">
+        <v>31</v>
+      </c>
+      <c r="AH16">
+        <v>73</v>
+      </c>
+      <c r="AI16" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ16">
+        <v>42</v>
+      </c>
+      <c r="AK16">
+        <v>36</v>
+      </c>
+      <c r="AL16">
+        <v>78</v>
+      </c>
+      <c r="AM16" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>9</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Aliya M Mulla</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2KD24CS008</v>
+      </c>
+      <c r="D17">
+        <v>43</v>
+      </c>
+      <c r="E17">
+        <v>49</v>
+      </c>
+      <c r="F17">
         <v>92</v>
       </c>
-      <c r="D6">
+      <c r="G17" t="str">
+        <v>P</v>
+      </c>
+      <c r="H17">
+        <v>43</v>
+      </c>
+      <c r="I17">
+        <v>29</v>
+      </c>
+      <c r="J17">
+        <v>72</v>
+      </c>
+      <c r="K17" t="str">
+        <v>P</v>
+      </c>
+      <c r="L17">
+        <v>43</v>
+      </c>
+      <c r="M17">
+        <v>34</v>
+      </c>
+      <c r="N17">
+        <v>77</v>
+      </c>
+      <c r="O17" t="str">
+        <v>P</v>
+      </c>
+      <c r="P17">
+        <v>43</v>
+      </c>
+      <c r="Q17">
+        <v>39</v>
+      </c>
+      <c r="R17">
+        <v>82</v>
+      </c>
+      <c r="S17" t="str">
+        <v>P</v>
+      </c>
+      <c r="T17">
+        <v>43</v>
+      </c>
+      <c r="U17">
+        <v>44</v>
+      </c>
+      <c r="V17">
+        <v>87</v>
+      </c>
+      <c r="W17" t="str">
+        <v>P</v>
+      </c>
+      <c r="X17">
+        <v>43</v>
+      </c>
+      <c r="Y17">
+        <v>49</v>
+      </c>
+      <c r="Z17">
+        <v>92</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB17">
+        <v>43</v>
+      </c>
+      <c r="AC17">
+        <v>29</v>
+      </c>
+      <c r="AD17">
+        <v>72</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF17">
+        <v>43</v>
+      </c>
+      <c r="AG17">
+        <v>34</v>
+      </c>
+      <c r="AH17">
+        <v>77</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ17">
+        <v>43</v>
+      </c>
+      <c r="AK17">
+        <v>39</v>
+      </c>
+      <c r="AL17">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Ama A Halappanavar</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2KD24CS009</v>
+      </c>
+      <c r="D18">
+        <v>44</v>
+      </c>
+      <c r="E18">
+        <v>27</v>
+      </c>
+      <c r="F18">
+        <v>71</v>
+      </c>
+      <c r="G18" t="str">
+        <v>P</v>
+      </c>
+      <c r="H18">
+        <v>44</v>
+      </c>
+      <c r="I18">
+        <v>32</v>
+      </c>
+      <c r="J18">
+        <v>76</v>
+      </c>
+      <c r="K18" t="str">
+        <v>P</v>
+      </c>
+      <c r="L18">
+        <v>44</v>
+      </c>
+      <c r="M18">
+        <v>37</v>
+      </c>
+      <c r="N18">
+        <v>81</v>
+      </c>
+      <c r="O18" t="str">
+        <v>P</v>
+      </c>
+      <c r="P18">
+        <v>44</v>
+      </c>
+      <c r="Q18">
+        <v>42</v>
+      </c>
+      <c r="R18">
+        <v>86</v>
+      </c>
+      <c r="S18" t="str">
+        <v>P</v>
+      </c>
+      <c r="T18">
+        <v>44</v>
+      </c>
+      <c r="U18">
+        <v>47</v>
+      </c>
+      <c r="V18">
+        <v>91</v>
+      </c>
+      <c r="W18" t="str">
+        <v>P</v>
+      </c>
+      <c r="X18">
+        <v>44</v>
+      </c>
+      <c r="Y18">
+        <v>27</v>
+      </c>
+      <c r="Z18">
+        <v>71</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB18">
+        <v>44</v>
+      </c>
+      <c r="AC18">
+        <v>32</v>
+      </c>
+      <c r="AD18">
+        <v>76</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF18">
+        <v>44</v>
+      </c>
+      <c r="AG18">
+        <v>37</v>
+      </c>
+      <c r="AH18">
+        <v>81</v>
+      </c>
+      <c r="AI18" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ18">
+        <v>44</v>
+      </c>
+      <c r="AK18">
+        <v>42</v>
+      </c>
+      <c r="AL18">
+        <v>86</v>
+      </c>
+      <c r="AM18" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>11</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Balaji P Khot</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2KD24CS020</v>
+      </c>
+      <c r="D19">
+        <v>45</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>57</v>
+      </c>
+      <c r="G19" t="str">
+        <v>P</v>
+      </c>
+      <c r="H19">
+        <v>45</v>
+      </c>
+      <c r="I19">
+        <v>35</v>
+      </c>
+      <c r="J19">
+        <v>80</v>
+      </c>
+      <c r="K19" t="str">
+        <v>P</v>
+      </c>
+      <c r="L19">
+        <v>45</v>
+      </c>
+      <c r="M19">
+        <v>40</v>
+      </c>
+      <c r="N19">
+        <v>85</v>
+      </c>
+      <c r="O19" t="str">
+        <v>P</v>
+      </c>
+      <c r="P19">
+        <v>45</v>
+      </c>
+      <c r="Q19">
+        <v>45</v>
+      </c>
+      <c r="R19">
+        <v>90</v>
+      </c>
+      <c r="S19" t="str">
+        <v>P</v>
+      </c>
+      <c r="T19">
+        <v>45</v>
+      </c>
+      <c r="U19">
+        <v>25</v>
+      </c>
+      <c r="V19">
+        <v>70</v>
+      </c>
+      <c r="W19" t="str">
+        <v>P</v>
+      </c>
+      <c r="X19">
+        <v>45</v>
+      </c>
+      <c r="Y19">
+        <v>30</v>
+      </c>
+      <c r="Z19">
+        <v>75</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB19">
+        <v>45</v>
+      </c>
+      <c r="AC19">
+        <v>35</v>
+      </c>
+      <c r="AD19">
+        <v>80</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF19">
+        <v>45</v>
+      </c>
+      <c r="AG19">
+        <v>40</v>
+      </c>
+      <c r="AH19">
+        <v>85</v>
+      </c>
+      <c r="AI19" t="str">
+        <v>A</v>
+      </c>
+      <c r="AJ19">
+        <v>45</v>
+      </c>
+      <c r="AK19">
+        <v>45</v>
+      </c>
+      <c r="AL19">
+        <v>90</v>
+      </c>
+      <c r="AM19" t="str">
+        <v>P</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>12</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Basavaraj Kagale</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2KD24CS021</v>
+      </c>
+      <c r="D20">
+        <v>46</v>
+      </c>
+      <c r="E20">
+        <v>33</v>
+      </c>
+      <c r="F20">
+        <v>79</v>
+      </c>
+      <c r="G20" t="str">
+        <v>P</v>
+      </c>
+      <c r="H20">
+        <v>46</v>
+      </c>
+      <c r="I20">
+        <v>38</v>
+      </c>
+      <c r="J20">
+        <v>84</v>
+      </c>
+      <c r="K20" t="str">
+        <v>P</v>
+      </c>
+      <c r="L20">
+        <v>46</v>
+      </c>
+      <c r="M20">
+        <v>43</v>
+      </c>
+      <c r="N20">
+        <v>89</v>
+      </c>
+      <c r="O20" t="str">
+        <v>P</v>
+      </c>
+      <c r="P20">
+        <v>46</v>
+      </c>
+      <c r="Q20">
+        <v>48</v>
+      </c>
+      <c r="R20">
         <v>94</v>
       </c>
-      <c r="E6">
+      <c r="S20" t="str">
+        <v>P</v>
+      </c>
+      <c r="T20">
+        <v>46</v>
+      </c>
+      <c r="U20">
+        <v>28</v>
+      </c>
+      <c r="V20">
+        <v>74</v>
+      </c>
+      <c r="W20" t="str">
+        <v>P</v>
+      </c>
+      <c r="X20">
+        <v>46</v>
+      </c>
+      <c r="Y20">
+        <v>33</v>
+      </c>
+      <c r="Z20">
+        <v>79</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>P</v>
+      </c>
+      <c r="AB20">
+        <v>46</v>
+      </c>
+      <c r="AC20">
+        <v>38</v>
+      </c>
+      <c r="AD20">
+        <v>84</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>P</v>
+      </c>
+      <c r="AF20">
+        <v>46</v>
+      </c>
+      <c r="AG20">
+        <v>43</v>
+      </c>
+      <c r="AH20">
         <v>89</v>
+      </c>
+      <c r="AI20" t="str">
+        <v>P</v>
+      </c>
+      <c r="AJ20">
+        <v>46</v>
+      </c>
+      <c r="AK20">
+        <v>48</v>
+      </c>
+      <c r="AL20">
+        <v>94</v>
+      </c>
+      <c r="AM20" t="str">
+        <v>P</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AM20"/>
   </ignoredErrors>
 </worksheet>
 </file>